--- a/file_operation/difflib/string_comparison/process/output_test/result_split_list_target_wb_d.xlsx
+++ b/file_operation/difflib/string_comparison/process/output_test/result_split_list_target_wb_d.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develop\github\python_labo\file_operation\difflib\string_comparison\process\output_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD24CCB-D920-4BAF-A872-F78202D2BB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABC8CCA-2E1B-42DE-AFE9-3E681F018FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6580" yWindow="5220" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>KKKKXXXZZZZ</t>
+    <t>QQQQXXXZZZZ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
